--- a/filer/37425311_tui.xlsx
+++ b/filer/37425311_tui.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/10–30/9 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/37425311_tui.xlsx
+++ b/filer/37425311_tui.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +644,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1498,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2448,35 +2448,35 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
@@ -3494,19 +3494,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
@@ -3612,19 +3612,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
@@ -3922,6 +3922,13 @@
       <c r="F81" s="13">
         <f>IFERROR($F$29/($F$50+0)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3953,19 +3960,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -3975,19 +3982,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>487556</v>
+        <v>322949</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>322949</v>
+        <v>1219171</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1219171</v>
+        <v>1289840</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>1289840</v>
+        <v>1521665</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1521665</v>
+        <v>1653405</v>
       </c>
     </row>
     <row r="3">
@@ -3996,18 +4003,20 @@
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
+      <c r="B3" s="16" t="n">
+        <v>11829</v>
+      </c>
       <c r="C3" s="16" t="n">
-        <v>11829</v>
+        <v>5149</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>5149</v>
+        <v>0</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0</v>
+        <v>1254</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>1254</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4">
@@ -4028,18 +4037,20 @@
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
+      <c r="B5" s="16" t="n">
+        <v>357243</v>
+      </c>
       <c r="C5" s="16" t="n">
-        <v>357243</v>
+        <v>1220542</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>1220542</v>
+        <v>1257326</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>1257326</v>
+        <v>84477</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>84477</v>
+        <v>81102</v>
       </c>
     </row>
     <row r="6">
@@ -4049,19 +4060,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>17239</v>
+        <v>-22464</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>-22464</v>
+        <v>3778</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3778</v>
+        <v>32514</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>32514</v>
+        <v>33310</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>33310</v>
+        <v>-6350</v>
       </c>
     </row>
     <row r="7">
@@ -4070,18 +4081,20 @@
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="16" t="n">
+        <v>23041</v>
+      </c>
       <c r="C7" s="16" t="n">
-        <v>23041</v>
+        <v>32030</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>32030</v>
+        <v>38530</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>38530</v>
+        <v>43865</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>43865</v>
+        <v>42999</v>
       </c>
     </row>
     <row r="8">
@@ -4097,18 +4110,20 @@
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="16" t="n">
+        <v>386</v>
+      </c>
       <c r="C9" s="16" t="n">
-        <v>386</v>
+        <v>329</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>209</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -4130,19 +4145,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>-7259</v>
+        <v>-45890</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-45890</v>
+        <v>-28581</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>-28581</v>
+        <v>-6324</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-6324</v>
+        <v>-10764</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-10764</v>
+        <v>-49421</v>
       </c>
     </row>
     <row r="12">
@@ -4163,18 +4178,20 @@
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" s="16" t="n">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>469</v>
+        <v>6862</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>6862</v>
+        <v>10239</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>10239</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="14">
@@ -4183,18 +4200,20 @@
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
+      <c r="B14" s="16" t="n">
+        <v>624</v>
+      </c>
       <c r="C14" s="16" t="n">
+        <v>222</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>847</v>
+      </c>
+      <c r="E14" s="16" t="n">
         <v>624</v>
       </c>
-      <c r="D14" s="16" t="n">
-        <v>222</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>847</v>
-      </c>
       <c r="F14" s="16" t="n">
-        <v>624</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="15">
@@ -4203,16 +4222,14 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>-126</v>
-      </c>
-      <c r="C15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n">
+        <v>-222</v>
+      </c>
       <c r="D15" s="16" t="n">
-        <v>-222</v>
-      </c>
-      <c r="E15" s="16" t="n">
         <v>6016</v>
       </c>
+      <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
     </row>
     <row r="16">
@@ -4222,19 +4239,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>-7385</v>
+        <v>-46514</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>-46514</v>
+        <v>-28334</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>-28334</v>
+        <v>-309</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-309</v>
+        <v>-1149</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>-1149</v>
+        <v>-43173</v>
       </c>
     </row>
     <row r="17">
@@ -4243,18 +4260,20 @@
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="16" t="n">
+        <v>-322</v>
+      </c>
       <c r="C17" s="16" t="n">
-        <v>-322</v>
+        <v>3987</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3987</v>
+        <v>-7156</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-7156</v>
+        <v>0</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0</v>
+        <v>10411</v>
       </c>
     </row>
     <row r="18">
@@ -4263,18 +4282,20 @@
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="16" t="n">
+        <v>-46192</v>
+      </c>
       <c r="C18" s="16" t="n">
-        <v>-46192</v>
+        <v>-32322</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>-32322</v>
+        <v>6847</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>6847</v>
+        <v>-1149</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>-1149</v>
+        <v>-53584</v>
       </c>
     </row>
     <row r="19">
@@ -4284,19 +4305,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -4305,16 +4326,14 @@
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n">
+        <v>128035</v>
+      </c>
       <c r="D20" s="16" t="n">
-        <v>128035</v>
-      </c>
-      <c r="E20" s="16" t="n">
         <v>96</v>
       </c>
+      <c r="E20" s="16" t="n"/>
       <c r="F20" s="16" t="n"/>
     </row>
   </sheetData>
@@ -4346,19 +4365,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4391,18 +4410,20 @@
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
+      <c r="B4" s="16" t="n">
+        <v>742</v>
+      </c>
       <c r="C4" s="16" t="n">
-        <v>742</v>
+        <v>542</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>542</v>
+        <v>330</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
@@ -4435,18 +4456,20 @@
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="16" t="n">
+        <v>742</v>
+      </c>
       <c r="C7" s="16" t="n">
-        <v>742</v>
+        <v>542</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>542</v>
+        <v>330</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -4455,18 +4478,20 @@
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
+      <c r="B8" s="16" t="n">
+        <v>742</v>
+      </c>
       <c r="C8" s="16" t="n">
-        <v>742</v>
+        <v>542</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>542</v>
+        <v>330</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -4475,16 +4500,16 @@
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="16" t="n">
+        <v>1460</v>
+      </c>
       <c r="C9" s="16" t="n">
-        <v>1460</v>
+        <v>9</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="E9" s="16" t="n"/>
       <c r="F9" s="16" t="n"/>
     </row>
     <row r="10">
@@ -4493,18 +4518,20 @@
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
+      <c r="B10" s="16" t="n">
+        <v>198432</v>
+      </c>
       <c r="C10" s="16" t="n">
-        <v>198432</v>
+        <v>91271</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>91271</v>
+        <v>141766</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>141766</v>
+        <v>26997</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>26997</v>
+        <v>111668</v>
       </c>
     </row>
     <row r="11">
@@ -4513,18 +4540,20 @@
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
+      <c r="B11" s="16" t="n">
+        <v>5313</v>
+      </c>
       <c r="C11" s="16" t="n">
-        <v>5313</v>
+        <v>4470</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>4470</v>
+        <v>15724</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>15724</v>
+        <v>21975</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>21975</v>
+        <v>14788</v>
       </c>
     </row>
     <row r="12">
@@ -4533,18 +4562,20 @@
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="16" t="n">
+        <v>3366</v>
+      </c>
       <c r="C12" s="16" t="n">
-        <v>3366</v>
+        <v>15776</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>15776</v>
+        <v>18630</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>18630</v>
+        <v>29727</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>29727</v>
+        <v>39693</v>
       </c>
     </row>
     <row r="13">
@@ -4553,18 +4584,20 @@
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="16" t="n">
+        <v>5002</v>
+      </c>
       <c r="C13" s="16" t="n">
         <v>5002</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>5002</v>
+        <v>10411</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>10411</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>10411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4575,10 +4608,10 @@
       </c>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
     </row>
     <row r="15">
@@ -4587,13 +4620,13 @@
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="16" t="n">
+        <v>302</v>
+      </c>
       <c r="C15" s="16" t="n">
-        <v>302</v>
-      </c>
-      <c r="D15" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
     </row>
@@ -4603,18 +4636,20 @@
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
+      <c r="B16" s="16" t="n">
+        <v>214204</v>
+      </c>
       <c r="C16" s="16" t="n">
-        <v>214204</v>
+        <v>118694</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>118694</v>
+        <v>186775</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>186775</v>
+        <v>89109</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>89109</v>
+        <v>166149</v>
       </c>
     </row>
     <row r="17">
@@ -4635,18 +4670,20 @@
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="16" t="n">
+        <v>102000</v>
+      </c>
       <c r="C18" s="16" t="n">
-        <v>102000</v>
+        <v>234400</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>234400</v>
+        <v>169885</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>169885</v>
+        <v>247058</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>247058</v>
+        <v>272058</v>
       </c>
     </row>
     <row r="19">
@@ -4655,18 +4692,20 @@
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="16" t="n">
+        <v>316204</v>
+      </c>
       <c r="C19" s="16" t="n">
-        <v>316204</v>
+        <v>353094</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>353094</v>
+        <v>356660</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>356660</v>
+        <v>336167</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>336167</v>
+        <v>438207</v>
       </c>
     </row>
     <row r="20">
@@ -4676,19 +4715,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>175393</v>
+        <v>316946</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>316946</v>
+        <v>353636</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>353636</v>
+        <v>356989</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>356989</v>
+        <v>336327</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>336327</v>
+        <v>438295</v>
       </c>
     </row>
     <row r="21">
@@ -4697,7 +4736,9 @@
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="16" t="n">
+        <v>1500</v>
+      </c>
       <c r="C21" s="16" t="n">
         <v>1500</v>
       </c>
@@ -4753,7 +4794,9 @@
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="16" t="n">
+        <v>3619</v>
+      </c>
       <c r="C25" s="16" t="n">
         <v>3619</v>
       </c>
@@ -4761,7 +4804,7 @@
         <v>3619</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>3619</v>
+        <v>0</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>0</v>
@@ -4773,18 +4816,20 @@
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
+      <c r="B26" s="16" t="n">
+        <v>42722</v>
+      </c>
       <c r="C26" s="16" t="n">
-        <v>42722</v>
+        <v>10406</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>10406</v>
+        <v>17248</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>17248</v>
+        <v>19719</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>19719</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="27">
@@ -4794,19 +4839,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>94040</v>
+        <v>47842</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>47842</v>
+        <v>15525</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>15525</v>
+        <v>22368</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>22368</v>
+        <v>21219</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>21219</v>
+        <v>7634</v>
       </c>
     </row>
     <row r="28">
@@ -4863,18 +4908,20 @@
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
+      <c r="B32" s="16" t="n">
+        <v>4555</v>
+      </c>
       <c r="C32" s="16" t="n">
-        <v>4555</v>
+        <v>4320</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>4320</v>
+        <v>3308</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>3308</v>
+        <v>4169</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>4169</v>
+        <v>9849</v>
       </c>
     </row>
     <row r="33">
@@ -4883,18 +4930,20 @@
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
+      <c r="B33" s="16" t="n">
+        <v>90335</v>
+      </c>
       <c r="C33" s="16" t="n">
-        <v>90335</v>
+        <v>111172</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>111172</v>
+        <v>103984</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>103984</v>
+        <v>17677</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>17677</v>
+        <v>129644</v>
       </c>
     </row>
     <row r="34">
@@ -4915,13 +4964,13 @@
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
+      <c r="B35" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="16" t="n">
         <v>3951</v>
       </c>
+      <c r="D35" s="16" t="n"/>
       <c r="E35" s="16" t="n"/>
       <c r="F35" s="16" t="n"/>
     </row>
@@ -4933,7 +4982,9 @@
       </c>
       <c r="B36" s="16" t="n"/>
       <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
+      <c r="D36" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="16" t="n">
         <v>0</v>
       </c>
@@ -4947,18 +4998,20 @@
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="16" t="n">
+        <v>6553</v>
+      </c>
       <c r="C37" s="16" t="n">
-        <v>6553</v>
+        <v>4667</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>4667</v>
+        <v>13447</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>13447</v>
+        <v>11173</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>11173</v>
+        <v>11336</v>
       </c>
     </row>
     <row r="38">
@@ -4967,18 +5020,20 @@
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
+      <c r="B38" s="16" t="n">
+        <v>167662</v>
+      </c>
       <c r="C38" s="16" t="n">
-        <v>167662</v>
+        <v>214002</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>214002</v>
+        <v>213883</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>213883</v>
+        <v>282090</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>282090</v>
+        <v>279832</v>
       </c>
     </row>
     <row r="39">
@@ -4987,18 +5042,20 @@
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
+      <c r="B39" s="16" t="n">
+        <v>269104</v>
+      </c>
       <c r="C39" s="16" t="n">
-        <v>269104</v>
+        <v>338111</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>338111</v>
+        <v>334622</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>334622</v>
+        <v>315108</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>315108</v>
+        <v>430661</v>
       </c>
     </row>
     <row r="40">
@@ -5007,18 +5064,20 @@
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
+      <c r="B40" s="16" t="n">
+        <v>269104</v>
+      </c>
       <c r="C40" s="16" t="n">
-        <v>269104</v>
+        <v>338111</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>338111</v>
+        <v>334622</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>334622</v>
+        <v>315108</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>315108</v>
+        <v>430661</v>
       </c>
     </row>
     <row r="41">
@@ -5028,19 +5087,19 @@
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>175393</v>
+        <v>316946</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>316946</v>
+        <v>353636</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>353636</v>
+        <v>356989</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>356989</v>
+        <v>336327</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>336327</v>
+        <v>438295</v>
       </c>
     </row>
   </sheetData>
@@ -5079,13 +5138,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -5790,7 +5849,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -5908,7 +5967,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6084,7 +6143,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
